--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-01 14:14</t>
+    <t>تاريخ التصدير: 2026-03-07 08:33</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-07 08:33</t>
+    <t>تاريخ التصدير: 2026-03-07 09:21</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-07 09:21</t>
+    <t>تاريخ التصدير: 2026-03-08 11:22</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-08 11:22</t>
+    <t>تاريخ التصدير: 2026-03-08 12:55</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-08 12:55</t>
+    <t>تاريخ التصدير: 2026-03-10 08:34</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-10 08:34</t>
+    <t>تاريخ التصدير: 2026-03-11 10:34</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 10:34</t>
+    <t>تاريخ التصدير: 2026-03-11 11:05</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 11:05</t>
+    <t>تاريخ التصدير: 2026-03-11 11:59</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 11:59</t>
+    <t>تاريخ التصدير: 2026-03-11 12:40</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 12:40</t>
+    <t>تاريخ التصدير: 2026-03-11 13:34</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 13:34</t>
+    <t>تاريخ التصدير: 2026-03-11 15:06</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-11 15:06</t>
+    <t>تاريخ التصدير: 2026-03-14 08:45</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-14 08:45</t>
+    <t>تاريخ التصدير: 2026-03-14 09:21</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-14 09:21</t>
+    <t>تاريخ التصدير: 2026-03-15 11:47</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-15 11:47</t>
+    <t>تاريخ التصدير: 2026-03-15 12:41</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-15 12:41</t>
+    <t>تاريخ التصدير: 2026-03-17 09:01</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-17 09:01</t>
+    <t>تاريخ التصدير: 2026-04-04 08:45</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-04 08:45</t>
+    <t>تاريخ التصدير: 2026-04-04 09:13</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-04 09:13</t>
+    <t>تاريخ التصدير: 2026-04-04 09:34</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-04 09:34</t>
+    <t>تاريخ التصدير: 2026-04-04 10:05</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-04 10:05</t>
+    <t>تاريخ التصدير: 2026-04-05 09:29</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 09:29</t>
+    <t>تاريخ التصدير: 2026-04-05 09:58</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 09:58</t>
+    <t>تاريخ التصدير: 2026-04-05 10:08</t>
   </si>
 </sst>
 </file>

--- a/3sci_center.xlsx
+++ b/3sci_center.xlsx
@@ -908,7 +908,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-05 10:08</t>
+    <t>تاريخ التصدير: 2026-04-05 10:19</t>
   </si>
 </sst>
 </file>
